--- a/IAC IP25 - Machine Learning - RAID Log - Pranay Sunil Jagtap.xlsx
+++ b/IAC IP25 - Machine Learning - RAID Log - Pranay Sunil Jagtap.xlsx
@@ -226,7 +226,7 @@
     <t xml:space="preserve">Project Manager/Team Lead</t>
   </si>
   <si>
-    <t xml:space="preserve">The provided dataset have relevant features for target variable prediction</t>
+    <t xml:space="preserve">The provided dataset has relevant features for target variable prediction</t>
   </si>
   <si>
     <t xml:space="preserve">Impacts model’s capability to learn from the features, eventually resulting in poor generalization</t>
